--- a/docs/payment-schedule-templates/Payment Schedules - Customer Portal/Collection_Schedule_Template_84mo.xlsx
+++ b/docs/payment-schedule-templates/Payment Schedules - Customer Portal/Collection_Schedule_Template_84mo.xlsx
@@ -1307,20 +1307,55 @@
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="14">
-      <c r="A2" s="20" t="n"/>
-      <c r="B2" s="20" t="n"/>
-      <c r="C2" s="20" t="n"/>
-      <c r="D2" s="20" t="n"/>
-      <c r="E2" s="20" t="n"/>
-      <c r="F2" s="20" t="n"/>
-      <c r="G2" s="21" t="n"/>
-      <c r="H2" s="21" t="n"/>
-      <c r="I2" s="21" t="n"/>
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>{{########}}</t>
+        </is>
+      </c>
+      <c r="B2" s="20" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>Nyandoro</t>
+        </is>
+      </c>
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>+17785808657</t>
+        </is>
+      </c>
+      <c r="E2" s="20" t="inlineStr">
+        <is>
+          <t>alex@michaeltenable.com</t>
+        </is>
+      </c>
+      <c r="F2" s="20" t="inlineStr">
+        <is>
+          <t>Internal Tester</t>
+        </is>
+      </c>
+      <c r="G2" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="21" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I2" s="21" t="n">
+        <v>120000</v>
+      </c>
       <c r="J2" s="22" t="n">
         <v>84</v>
       </c>
-      <c r="K2" s="21" t="n"/>
-      <c r="L2" s="23" t="n"/>
+      <c r="K2" s="21">
+        <f>IF(J2=0,"",ROUND((I2-H2)/J2,2))</f>
+        <v/>
+      </c>
+      <c r="L2" s="23" t="n">
+        <v>46147</v>
+      </c>
       <c r="M2" s="21" t="n"/>
       <c r="N2" s="21" t="n"/>
       <c r="O2" s="21" t="n"/>
@@ -1407,15 +1442,15 @@
       <c r="CR2" s="21" t="n"/>
       <c r="CS2" s="21" t="n"/>
       <c r="CT2" s="24">
-        <f>SUM(M2:CR2)</f>
+        <f>H2+SUM(M2:CR2)</f>
         <v/>
       </c>
       <c r="CU2" s="24">
-        <f>I2-CT2</f>
+        <f>I2-H2-SUM(M2:CR2)</f>
         <v/>
       </c>
       <c r="CV2" s="25">
-        <f>IF(I2=0,"",CT2/I2)</f>
+        <f>IF(I2=0,"",(H2+SUM(M2:CR2))/I2)</f>
         <v/>
       </c>
       <c r="CW2" s="26" t="n"/>
@@ -1528,15 +1563,15 @@
       <c r="CR3" s="21" t="n"/>
       <c r="CS3" s="21" t="n"/>
       <c r="CT3" s="24">
-        <f>SUM(M3:CR3)</f>
+        <f>H3+SUM(M3:CR3)</f>
         <v/>
       </c>
       <c r="CU3" s="24">
-        <f>I3-CT3</f>
+        <f>I3-H3-SUM(M3:CR3)</f>
         <v/>
       </c>
       <c r="CV3" s="25">
-        <f>IF(I3=0,"",CT3/I3)</f>
+        <f>IF(I3=0,"",(H3+SUM(M3:CR3))/I3)</f>
         <v/>
       </c>
       <c r="CW3" s="26" t="n"/>
@@ -1649,15 +1684,15 @@
       <c r="CR4" s="21" t="n"/>
       <c r="CS4" s="21" t="n"/>
       <c r="CT4" s="24">
-        <f>SUM(M4:CR4)</f>
+        <f>H4+SUM(M4:CR4)</f>
         <v/>
       </c>
       <c r="CU4" s="24">
-        <f>I4-CT4</f>
+        <f>I4-H4-SUM(M4:CR4)</f>
         <v/>
       </c>
       <c r="CV4" s="25">
-        <f>IF(I4=0,"",CT4/I4)</f>
+        <f>IF(I4=0,"",(H4+SUM(M4:CR4))/I4)</f>
         <v/>
       </c>
       <c r="CW4" s="26" t="n"/>
@@ -1770,15 +1805,15 @@
       <c r="CR5" s="21" t="n"/>
       <c r="CS5" s="21" t="n"/>
       <c r="CT5" s="24">
-        <f>SUM(M5:CR5)</f>
+        <f>H5+SUM(M5:CR5)</f>
         <v/>
       </c>
       <c r="CU5" s="24">
-        <f>I5-CT5</f>
+        <f>I5-H5-SUM(M5:CR5)</f>
         <v/>
       </c>
       <c r="CV5" s="25">
-        <f>IF(I5=0,"",CT5/I5)</f>
+        <f>IF(I5=0,"",(H5+SUM(M5:CR5))/I5)</f>
         <v/>
       </c>
       <c r="CW5" s="26" t="n"/>
@@ -1891,15 +1926,15 @@
       <c r="CR6" s="21" t="n"/>
       <c r="CS6" s="21" t="n"/>
       <c r="CT6" s="24">
-        <f>SUM(M6:CR6)</f>
+        <f>H6+SUM(M6:CR6)</f>
         <v/>
       </c>
       <c r="CU6" s="24">
-        <f>I6-CT6</f>
+        <f>I6-H6-SUM(M6:CR6)</f>
         <v/>
       </c>
       <c r="CV6" s="25">
-        <f>IF(I6=0,"",CT6/I6)</f>
+        <f>IF(I6=0,"",(H6+SUM(M6:CR6))/I6)</f>
         <v/>
       </c>
       <c r="CW6" s="26" t="n"/>
@@ -2012,15 +2047,15 @@
       <c r="CR7" s="21" t="n"/>
       <c r="CS7" s="21" t="n"/>
       <c r="CT7" s="24">
-        <f>SUM(M7:CR7)</f>
+        <f>H7+SUM(M7:CR7)</f>
         <v/>
       </c>
       <c r="CU7" s="24">
-        <f>I7-CT7</f>
+        <f>I7-H7-SUM(M7:CR7)</f>
         <v/>
       </c>
       <c r="CV7" s="25">
-        <f>IF(I7=0,"",CT7/I7)</f>
+        <f>IF(I7=0,"",(H7+SUM(M7:CR7))/I7)</f>
         <v/>
       </c>
       <c r="CW7" s="26" t="n"/>
@@ -2133,15 +2168,15 @@
       <c r="CR8" s="21" t="n"/>
       <c r="CS8" s="21" t="n"/>
       <c r="CT8" s="24">
-        <f>SUM(M8:CR8)</f>
+        <f>H8+SUM(M8:CR8)</f>
         <v/>
       </c>
       <c r="CU8" s="24">
-        <f>I8-CT8</f>
+        <f>I8-H8-SUM(M8:CR8)</f>
         <v/>
       </c>
       <c r="CV8" s="25">
-        <f>IF(I8=0,"",CT8/I8)</f>
+        <f>IF(I8=0,"",(H8+SUM(M8:CR8))/I8)</f>
         <v/>
       </c>
       <c r="CW8" s="26" t="n"/>
@@ -2254,15 +2289,15 @@
       <c r="CR9" s="21" t="n"/>
       <c r="CS9" s="21" t="n"/>
       <c r="CT9" s="24">
-        <f>SUM(M9:CR9)</f>
+        <f>H9+SUM(M9:CR9)</f>
         <v/>
       </c>
       <c r="CU9" s="24">
-        <f>I9-CT9</f>
+        <f>I9-H9-SUM(M9:CR9)</f>
         <v/>
       </c>
       <c r="CV9" s="25">
-        <f>IF(I9=0,"",CT9/I9)</f>
+        <f>IF(I9=0,"",(H9+SUM(M9:CR9))/I9)</f>
         <v/>
       </c>
       <c r="CW9" s="26" t="n"/>
@@ -2375,15 +2410,15 @@
       <c r="CR10" s="21" t="n"/>
       <c r="CS10" s="21" t="n"/>
       <c r="CT10" s="24">
-        <f>SUM(M10:CR10)</f>
+        <f>H10+SUM(M10:CR10)</f>
         <v/>
       </c>
       <c r="CU10" s="24">
-        <f>I10-CT10</f>
+        <f>I10-H10-SUM(M10:CR10)</f>
         <v/>
       </c>
       <c r="CV10" s="25">
-        <f>IF(I10=0,"",CT10/I10)</f>
+        <f>IF(I10=0,"",(H10+SUM(M10:CR10))/I10)</f>
         <v/>
       </c>
       <c r="CW10" s="26" t="n"/>
@@ -2496,15 +2531,15 @@
       <c r="CR11" s="21" t="n"/>
       <c r="CS11" s="21" t="n"/>
       <c r="CT11" s="24">
-        <f>SUM(M11:CR11)</f>
+        <f>H11+SUM(M11:CR11)</f>
         <v/>
       </c>
       <c r="CU11" s="24">
-        <f>I11-CT11</f>
+        <f>I11-H11-SUM(M11:CR11)</f>
         <v/>
       </c>
       <c r="CV11" s="25">
-        <f>IF(I11=0,"",CT11/I11)</f>
+        <f>IF(I11=0,"",(H11+SUM(M11:CR11))/I11)</f>
         <v/>
       </c>
       <c r="CW11" s="26" t="n"/>
@@ -2617,15 +2652,15 @@
       <c r="CR12" s="21" t="n"/>
       <c r="CS12" s="21" t="n"/>
       <c r="CT12" s="24">
-        <f>SUM(M12:CR12)</f>
+        <f>H12+SUM(M12:CR12)</f>
         <v/>
       </c>
       <c r="CU12" s="24">
-        <f>I12-CT12</f>
+        <f>I12-H12-SUM(M12:CR12)</f>
         <v/>
       </c>
       <c r="CV12" s="25">
-        <f>IF(I12=0,"",CT12/I12)</f>
+        <f>IF(I12=0,"",(H12+SUM(M12:CR12))/I12)</f>
         <v/>
       </c>
       <c r="CW12" s="26" t="n"/>
@@ -2738,15 +2773,15 @@
       <c r="CR13" s="21" t="n"/>
       <c r="CS13" s="21" t="n"/>
       <c r="CT13" s="24">
-        <f>SUM(M13:CR13)</f>
+        <f>H13+SUM(M13:CR13)</f>
         <v/>
       </c>
       <c r="CU13" s="24">
-        <f>I13-CT13</f>
+        <f>I13-H13-SUM(M13:CR13)</f>
         <v/>
       </c>
       <c r="CV13" s="25">
-        <f>IF(I13=0,"",CT13/I13)</f>
+        <f>IF(I13=0,"",(H13+SUM(M13:CR13))/I13)</f>
         <v/>
       </c>
       <c r="CW13" s="26" t="n"/>
@@ -2859,15 +2894,15 @@
       <c r="CR14" s="21" t="n"/>
       <c r="CS14" s="21" t="n"/>
       <c r="CT14" s="24">
-        <f>SUM(M14:CR14)</f>
+        <f>H14+SUM(M14:CR14)</f>
         <v/>
       </c>
       <c r="CU14" s="24">
-        <f>I14-CT14</f>
+        <f>I14-H14-SUM(M14:CR14)</f>
         <v/>
       </c>
       <c r="CV14" s="25">
-        <f>IF(I14=0,"",CT14/I14)</f>
+        <f>IF(I14=0,"",(H14+SUM(M14:CR14))/I14)</f>
         <v/>
       </c>
       <c r="CW14" s="26" t="n"/>
@@ -2980,15 +3015,15 @@
       <c r="CR15" s="21" t="n"/>
       <c r="CS15" s="21" t="n"/>
       <c r="CT15" s="24">
-        <f>SUM(M15:CR15)</f>
+        <f>H15+SUM(M15:CR15)</f>
         <v/>
       </c>
       <c r="CU15" s="24">
-        <f>I15-CT15</f>
+        <f>I15-H15-SUM(M15:CR15)</f>
         <v/>
       </c>
       <c r="CV15" s="25">
-        <f>IF(I15=0,"",CT15/I15)</f>
+        <f>IF(I15=0,"",(H15+SUM(M15:CR15))/I15)</f>
         <v/>
       </c>
       <c r="CW15" s="26" t="n"/>
@@ -3101,15 +3136,15 @@
       <c r="CR16" s="21" t="n"/>
       <c r="CS16" s="21" t="n"/>
       <c r="CT16" s="24">
-        <f>SUM(M16:CR16)</f>
+        <f>H16+SUM(M16:CR16)</f>
         <v/>
       </c>
       <c r="CU16" s="24">
-        <f>I16-CT16</f>
+        <f>I16-H16-SUM(M16:CR16)</f>
         <v/>
       </c>
       <c r="CV16" s="25">
-        <f>IF(I16=0,"",CT16/I16)</f>
+        <f>IF(I16=0,"",(H16+SUM(M16:CR16))/I16)</f>
         <v/>
       </c>
       <c r="CW16" s="26" t="n"/>
@@ -3222,15 +3257,15 @@
       <c r="CR17" s="21" t="n"/>
       <c r="CS17" s="21" t="n"/>
       <c r="CT17" s="24">
-        <f>SUM(M17:CR17)</f>
+        <f>H17+SUM(M17:CR17)</f>
         <v/>
       </c>
       <c r="CU17" s="24">
-        <f>I17-CT17</f>
+        <f>I17-H17-SUM(M17:CR17)</f>
         <v/>
       </c>
       <c r="CV17" s="25">
-        <f>IF(I17=0,"",CT17/I17)</f>
+        <f>IF(I17=0,"",(H17+SUM(M17:CR17))/I17)</f>
         <v/>
       </c>
       <c r="CW17" s="26" t="n"/>
@@ -3343,15 +3378,15 @@
       <c r="CR18" s="21" t="n"/>
       <c r="CS18" s="21" t="n"/>
       <c r="CT18" s="24">
-        <f>SUM(M18:CR18)</f>
+        <f>H18+SUM(M18:CR18)</f>
         <v/>
       </c>
       <c r="CU18" s="24">
-        <f>I18-CT18</f>
+        <f>I18-H18-SUM(M18:CR18)</f>
         <v/>
       </c>
       <c r="CV18" s="25">
-        <f>IF(I18=0,"",CT18/I18)</f>
+        <f>IF(I18=0,"",(H18+SUM(M18:CR18))/I18)</f>
         <v/>
       </c>
       <c r="CW18" s="26" t="n"/>
@@ -3464,15 +3499,15 @@
       <c r="CR19" s="21" t="n"/>
       <c r="CS19" s="21" t="n"/>
       <c r="CT19" s="24">
-        <f>SUM(M19:CR19)</f>
+        <f>H19+SUM(M19:CR19)</f>
         <v/>
       </c>
       <c r="CU19" s="24">
-        <f>I19-CT19</f>
+        <f>I19-H19-SUM(M19:CR19)</f>
         <v/>
       </c>
       <c r="CV19" s="25">
-        <f>IF(I19=0,"",CT19/I19)</f>
+        <f>IF(I19=0,"",(H19+SUM(M19:CR19))/I19)</f>
         <v/>
       </c>
       <c r="CW19" s="26" t="n"/>
@@ -3585,15 +3620,15 @@
       <c r="CR20" s="21" t="n"/>
       <c r="CS20" s="21" t="n"/>
       <c r="CT20" s="24">
-        <f>SUM(M20:CR20)</f>
+        <f>H20+SUM(M20:CR20)</f>
         <v/>
       </c>
       <c r="CU20" s="24">
-        <f>I20-CT20</f>
+        <f>I20-H20-SUM(M20:CR20)</f>
         <v/>
       </c>
       <c r="CV20" s="25">
-        <f>IF(I20=0,"",CT20/I20)</f>
+        <f>IF(I20=0,"",(H20+SUM(M20:CR20))/I20)</f>
         <v/>
       </c>
       <c r="CW20" s="26" t="n"/>
@@ -3706,15 +3741,15 @@
       <c r="CR21" s="21" t="n"/>
       <c r="CS21" s="21" t="n"/>
       <c r="CT21" s="24">
-        <f>SUM(M21:CR21)</f>
+        <f>H21+SUM(M21:CR21)</f>
         <v/>
       </c>
       <c r="CU21" s="24">
-        <f>I21-CT21</f>
+        <f>I21-H21-SUM(M21:CR21)</f>
         <v/>
       </c>
       <c r="CV21" s="25">
-        <f>IF(I21=0,"",CT21/I21)</f>
+        <f>IF(I21=0,"",(H21+SUM(M21:CR21))/I21)</f>
         <v/>
       </c>
       <c r="CW21" s="26" t="n"/>
@@ -3827,15 +3862,15 @@
       <c r="CR22" s="21" t="n"/>
       <c r="CS22" s="21" t="n"/>
       <c r="CT22" s="24">
-        <f>SUM(M22:CR22)</f>
+        <f>H22+SUM(M22:CR22)</f>
         <v/>
       </c>
       <c r="CU22" s="24">
-        <f>I22-CT22</f>
+        <f>I22-H22-SUM(M22:CR22)</f>
         <v/>
       </c>
       <c r="CV22" s="25">
-        <f>IF(I22=0,"",CT22/I22)</f>
+        <f>IF(I22=0,"",(H22+SUM(M22:CR22))/I22)</f>
         <v/>
       </c>
       <c r="CW22" s="26" t="n"/>
@@ -3948,15 +3983,15 @@
       <c r="CR23" s="21" t="n"/>
       <c r="CS23" s="21" t="n"/>
       <c r="CT23" s="24">
-        <f>SUM(M23:CR23)</f>
+        <f>H23+SUM(M23:CR23)</f>
         <v/>
       </c>
       <c r="CU23" s="24">
-        <f>I23-CT23</f>
+        <f>I23-H23-SUM(M23:CR23)</f>
         <v/>
       </c>
       <c r="CV23" s="25">
-        <f>IF(I23=0,"",CT23/I23)</f>
+        <f>IF(I23=0,"",(H23+SUM(M23:CR23))/I23)</f>
         <v/>
       </c>
       <c r="CW23" s="26" t="n"/>
@@ -4069,15 +4104,15 @@
       <c r="CR24" s="21" t="n"/>
       <c r="CS24" s="21" t="n"/>
       <c r="CT24" s="24">
-        <f>SUM(M24:CR24)</f>
+        <f>H24+SUM(M24:CR24)</f>
         <v/>
       </c>
       <c r="CU24" s="24">
-        <f>I24-CT24</f>
+        <f>I24-H24-SUM(M24:CR24)</f>
         <v/>
       </c>
       <c r="CV24" s="25">
-        <f>IF(I24=0,"",CT24/I24)</f>
+        <f>IF(I24=0,"",(H24+SUM(M24:CR24))/I24)</f>
         <v/>
       </c>
       <c r="CW24" s="26" t="n"/>
@@ -4190,15 +4225,15 @@
       <c r="CR25" s="21" t="n"/>
       <c r="CS25" s="21" t="n"/>
       <c r="CT25" s="24">
-        <f>SUM(M25:CR25)</f>
+        <f>H25+SUM(M25:CR25)</f>
         <v/>
       </c>
       <c r="CU25" s="24">
-        <f>I25-CT25</f>
+        <f>I25-H25-SUM(M25:CR25)</f>
         <v/>
       </c>
       <c r="CV25" s="25">
-        <f>IF(I25=0,"",CT25/I25)</f>
+        <f>IF(I25=0,"",(H25+SUM(M25:CR25))/I25)</f>
         <v/>
       </c>
       <c r="CW25" s="26" t="n"/>
@@ -4311,15 +4346,15 @@
       <c r="CR26" s="21" t="n"/>
       <c r="CS26" s="21" t="n"/>
       <c r="CT26" s="24">
-        <f>SUM(M26:CR26)</f>
+        <f>H26+SUM(M26:CR26)</f>
         <v/>
       </c>
       <c r="CU26" s="24">
-        <f>I26-CT26</f>
+        <f>I26-H26-SUM(M26:CR26)</f>
         <v/>
       </c>
       <c r="CV26" s="25">
-        <f>IF(I26=0,"",CT26/I26)</f>
+        <f>IF(I26=0,"",(H26+SUM(M26:CR26))/I26)</f>
         <v/>
       </c>
       <c r="CW26" s="26" t="n"/>
@@ -4432,15 +4467,15 @@
       <c r="CR27" s="21" t="n"/>
       <c r="CS27" s="21" t="n"/>
       <c r="CT27" s="24">
-        <f>SUM(M27:CR27)</f>
+        <f>H27+SUM(M27:CR27)</f>
         <v/>
       </c>
       <c r="CU27" s="24">
-        <f>I27-CT27</f>
+        <f>I27-H27-SUM(M27:CR27)</f>
         <v/>
       </c>
       <c r="CV27" s="25">
-        <f>IF(I27=0,"",CT27/I27)</f>
+        <f>IF(I27=0,"",(H27+SUM(M27:CR27))/I27)</f>
         <v/>
       </c>
       <c r="CW27" s="26" t="n"/>
@@ -4553,15 +4588,15 @@
       <c r="CR28" s="21" t="n"/>
       <c r="CS28" s="21" t="n"/>
       <c r="CT28" s="24">
-        <f>SUM(M28:CR28)</f>
+        <f>H28+SUM(M28:CR28)</f>
         <v/>
       </c>
       <c r="CU28" s="24">
-        <f>I28-CT28</f>
+        <f>I28-H28-SUM(M28:CR28)</f>
         <v/>
       </c>
       <c r="CV28" s="25">
-        <f>IF(I28=0,"",CT28/I28)</f>
+        <f>IF(I28=0,"",(H28+SUM(M28:CR28))/I28)</f>
         <v/>
       </c>
       <c r="CW28" s="26" t="n"/>
@@ -4674,15 +4709,15 @@
       <c r="CR29" s="21" t="n"/>
       <c r="CS29" s="21" t="n"/>
       <c r="CT29" s="24">
-        <f>SUM(M29:CR29)</f>
+        <f>H29+SUM(M29:CR29)</f>
         <v/>
       </c>
       <c r="CU29" s="24">
-        <f>I29-CT29</f>
+        <f>I29-H29-SUM(M29:CR29)</f>
         <v/>
       </c>
       <c r="CV29" s="25">
-        <f>IF(I29=0,"",CT29/I29)</f>
+        <f>IF(I29=0,"",(H29+SUM(M29:CR29))/I29)</f>
         <v/>
       </c>
       <c r="CW29" s="26" t="n"/>
@@ -4795,15 +4830,15 @@
       <c r="CR30" s="21" t="n"/>
       <c r="CS30" s="21" t="n"/>
       <c r="CT30" s="24">
-        <f>SUM(M30:CR30)</f>
+        <f>H30+SUM(M30:CR30)</f>
         <v/>
       </c>
       <c r="CU30" s="24">
-        <f>I30-CT30</f>
+        <f>I30-H30-SUM(M30:CR30)</f>
         <v/>
       </c>
       <c r="CV30" s="25">
-        <f>IF(I30=0,"",CT30/I30)</f>
+        <f>IF(I30=0,"",(H30+SUM(M30:CR30))/I30)</f>
         <v/>
       </c>
       <c r="CW30" s="26" t="n"/>
@@ -4916,15 +4951,15 @@
       <c r="CR31" s="21" t="n"/>
       <c r="CS31" s="21" t="n"/>
       <c r="CT31" s="24">
-        <f>SUM(M31:CR31)</f>
+        <f>H31+SUM(M31:CR31)</f>
         <v/>
       </c>
       <c r="CU31" s="24">
-        <f>I31-CT31</f>
+        <f>I31-H31-SUM(M31:CR31)</f>
         <v/>
       </c>
       <c r="CV31" s="25">
-        <f>IF(I31=0,"",CT31/I31)</f>
+        <f>IF(I31=0,"",(H31+SUM(M31:CR31))/I31)</f>
         <v/>
       </c>
       <c r="CW31" s="26" t="n"/>
@@ -5037,15 +5072,15 @@
       <c r="CR32" s="21" t="n"/>
       <c r="CS32" s="21" t="n"/>
       <c r="CT32" s="24">
-        <f>SUM(M32:CR32)</f>
+        <f>H32+SUM(M32:CR32)</f>
         <v/>
       </c>
       <c r="CU32" s="24">
-        <f>I32-CT32</f>
+        <f>I32-H32-SUM(M32:CR32)</f>
         <v/>
       </c>
       <c r="CV32" s="25">
-        <f>IF(I32=0,"",CT32/I32)</f>
+        <f>IF(I32=0,"",(H32+SUM(M32:CR32))/I32)</f>
         <v/>
       </c>
       <c r="CW32" s="26" t="n"/>
@@ -5158,15 +5193,15 @@
       <c r="CR33" s="21" t="n"/>
       <c r="CS33" s="21" t="n"/>
       <c r="CT33" s="24">
-        <f>SUM(M33:CR33)</f>
+        <f>H33+SUM(M33:CR33)</f>
         <v/>
       </c>
       <c r="CU33" s="24">
-        <f>I33-CT33</f>
+        <f>I33-H33-SUM(M33:CR33)</f>
         <v/>
       </c>
       <c r="CV33" s="25">
-        <f>IF(I33=0,"",CT33/I33)</f>
+        <f>IF(I33=0,"",(H33+SUM(M33:CR33))/I33)</f>
         <v/>
       </c>
       <c r="CW33" s="26" t="n"/>
@@ -5279,15 +5314,15 @@
       <c r="CR34" s="21" t="n"/>
       <c r="CS34" s="21" t="n"/>
       <c r="CT34" s="24">
-        <f>SUM(M34:CR34)</f>
+        <f>H34+SUM(M34:CR34)</f>
         <v/>
       </c>
       <c r="CU34" s="24">
-        <f>I34-CT34</f>
+        <f>I34-H34-SUM(M34:CR34)</f>
         <v/>
       </c>
       <c r="CV34" s="25">
-        <f>IF(I34=0,"",CT34/I34)</f>
+        <f>IF(I34=0,"",(H34+SUM(M34:CR34))/I34)</f>
         <v/>
       </c>
       <c r="CW34" s="26" t="n"/>
@@ -5400,15 +5435,15 @@
       <c r="CR35" s="21" t="n"/>
       <c r="CS35" s="21" t="n"/>
       <c r="CT35" s="24">
-        <f>SUM(M35:CR35)</f>
+        <f>H35+SUM(M35:CR35)</f>
         <v/>
       </c>
       <c r="CU35" s="24">
-        <f>I35-CT35</f>
+        <f>I35-H35-SUM(M35:CR35)</f>
         <v/>
       </c>
       <c r="CV35" s="25">
-        <f>IF(I35=0,"",CT35/I35)</f>
+        <f>IF(I35=0,"",(H35+SUM(M35:CR35))/I35)</f>
         <v/>
       </c>
       <c r="CW35" s="26" t="n"/>
@@ -5521,15 +5556,15 @@
       <c r="CR36" s="21" t="n"/>
       <c r="CS36" s="21" t="n"/>
       <c r="CT36" s="24">
-        <f>SUM(M36:CR36)</f>
+        <f>H36+SUM(M36:CR36)</f>
         <v/>
       </c>
       <c r="CU36" s="24">
-        <f>I36-CT36</f>
+        <f>I36-H36-SUM(M36:CR36)</f>
         <v/>
       </c>
       <c r="CV36" s="25">
-        <f>IF(I36=0,"",CT36/I36)</f>
+        <f>IF(I36=0,"",(H36+SUM(M36:CR36))/I36)</f>
         <v/>
       </c>
       <c r="CW36" s="26" t="n"/>
@@ -5642,15 +5677,15 @@
       <c r="CR37" s="21" t="n"/>
       <c r="CS37" s="21" t="n"/>
       <c r="CT37" s="24">
-        <f>SUM(M37:CR37)</f>
+        <f>H37+SUM(M37:CR37)</f>
         <v/>
       </c>
       <c r="CU37" s="24">
-        <f>I37-CT37</f>
+        <f>I37-H37-SUM(M37:CR37)</f>
         <v/>
       </c>
       <c r="CV37" s="25">
-        <f>IF(I37=0,"",CT37/I37)</f>
+        <f>IF(I37=0,"",(H37+SUM(M37:CR37))/I37)</f>
         <v/>
       </c>
       <c r="CW37" s="26" t="n"/>
@@ -5763,15 +5798,15 @@
       <c r="CR38" s="21" t="n"/>
       <c r="CS38" s="21" t="n"/>
       <c r="CT38" s="24">
-        <f>SUM(M38:CR38)</f>
+        <f>H38+SUM(M38:CR38)</f>
         <v/>
       </c>
       <c r="CU38" s="24">
-        <f>I38-CT38</f>
+        <f>I38-H38-SUM(M38:CR38)</f>
         <v/>
       </c>
       <c r="CV38" s="25">
-        <f>IF(I38=0,"",CT38/I38)</f>
+        <f>IF(I38=0,"",(H38+SUM(M38:CR38))/I38)</f>
         <v/>
       </c>
       <c r="CW38" s="26" t="n"/>
@@ -5884,15 +5919,15 @@
       <c r="CR39" s="21" t="n"/>
       <c r="CS39" s="21" t="n"/>
       <c r="CT39" s="24">
-        <f>SUM(M39:CR39)</f>
+        <f>H39+SUM(M39:CR39)</f>
         <v/>
       </c>
       <c r="CU39" s="24">
-        <f>I39-CT39</f>
+        <f>I39-H39-SUM(M39:CR39)</f>
         <v/>
       </c>
       <c r="CV39" s="25">
-        <f>IF(I39=0,"",CT39/I39)</f>
+        <f>IF(I39=0,"",(H39+SUM(M39:CR39))/I39)</f>
         <v/>
       </c>
       <c r="CW39" s="26" t="n"/>
@@ -6005,15 +6040,15 @@
       <c r="CR40" s="21" t="n"/>
       <c r="CS40" s="21" t="n"/>
       <c r="CT40" s="24">
-        <f>SUM(M40:CR40)</f>
+        <f>H40+SUM(M40:CR40)</f>
         <v/>
       </c>
       <c r="CU40" s="24">
-        <f>I40-CT40</f>
+        <f>I40-H40-SUM(M40:CR40)</f>
         <v/>
       </c>
       <c r="CV40" s="25">
-        <f>IF(I40=0,"",CT40/I40)</f>
+        <f>IF(I40=0,"",(H40+SUM(M40:CR40))/I40)</f>
         <v/>
       </c>
       <c r="CW40" s="26" t="n"/>
@@ -6126,15 +6161,15 @@
       <c r="CR41" s="21" t="n"/>
       <c r="CS41" s="21" t="n"/>
       <c r="CT41" s="24">
-        <f>SUM(M41:CR41)</f>
+        <f>H41+SUM(M41:CR41)</f>
         <v/>
       </c>
       <c r="CU41" s="24">
-        <f>I41-CT41</f>
+        <f>I41-H41-SUM(M41:CR41)</f>
         <v/>
       </c>
       <c r="CV41" s="25">
-        <f>IF(I41=0,"",CT41/I41)</f>
+        <f>IF(I41=0,"",(H41+SUM(M41:CR41))/I41)</f>
         <v/>
       </c>
       <c r="CW41" s="26" t="n"/>
@@ -6247,15 +6282,15 @@
       <c r="CR42" s="21" t="n"/>
       <c r="CS42" s="21" t="n"/>
       <c r="CT42" s="24">
-        <f>SUM(M42:CR42)</f>
+        <f>H42+SUM(M42:CR42)</f>
         <v/>
       </c>
       <c r="CU42" s="24">
-        <f>I42-CT42</f>
+        <f>I42-H42-SUM(M42:CR42)</f>
         <v/>
       </c>
       <c r="CV42" s="25">
-        <f>IF(I42=0,"",CT42/I42)</f>
+        <f>IF(I42=0,"",(H42+SUM(M42:CR42))/I42)</f>
         <v/>
       </c>
       <c r="CW42" s="26" t="n"/>
@@ -6368,15 +6403,15 @@
       <c r="CR43" s="21" t="n"/>
       <c r="CS43" s="21" t="n"/>
       <c r="CT43" s="24">
-        <f>SUM(M43:CR43)</f>
+        <f>H43+SUM(M43:CR43)</f>
         <v/>
       </c>
       <c r="CU43" s="24">
-        <f>I43-CT43</f>
+        <f>I43-H43-SUM(M43:CR43)</f>
         <v/>
       </c>
       <c r="CV43" s="25">
-        <f>IF(I43=0,"",CT43/I43)</f>
+        <f>IF(I43=0,"",(H43+SUM(M43:CR43))/I43)</f>
         <v/>
       </c>
       <c r="CW43" s="26" t="n"/>
@@ -6489,15 +6524,15 @@
       <c r="CR44" s="21" t="n"/>
       <c r="CS44" s="21" t="n"/>
       <c r="CT44" s="24">
-        <f>SUM(M44:CR44)</f>
+        <f>H44+SUM(M44:CR44)</f>
         <v/>
       </c>
       <c r="CU44" s="24">
-        <f>I44-CT44</f>
+        <f>I44-H44-SUM(M44:CR44)</f>
         <v/>
       </c>
       <c r="CV44" s="25">
-        <f>IF(I44=0,"",CT44/I44)</f>
+        <f>IF(I44=0,"",(H44+SUM(M44:CR44))/I44)</f>
         <v/>
       </c>
       <c r="CW44" s="26" t="n"/>
@@ -6610,15 +6645,15 @@
       <c r="CR45" s="21" t="n"/>
       <c r="CS45" s="21" t="n"/>
       <c r="CT45" s="24">
-        <f>SUM(M45:CR45)</f>
+        <f>H45+SUM(M45:CR45)</f>
         <v/>
       </c>
       <c r="CU45" s="24">
-        <f>I45-CT45</f>
+        <f>I45-H45-SUM(M45:CR45)</f>
         <v/>
       </c>
       <c r="CV45" s="25">
-        <f>IF(I45=0,"",CT45/I45)</f>
+        <f>IF(I45=0,"",(H45+SUM(M45:CR45))/I45)</f>
         <v/>
       </c>
       <c r="CW45" s="26" t="n"/>
@@ -6731,15 +6766,15 @@
       <c r="CR46" s="21" t="n"/>
       <c r="CS46" s="21" t="n"/>
       <c r="CT46" s="24">
-        <f>SUM(M46:CR46)</f>
+        <f>H46+SUM(M46:CR46)</f>
         <v/>
       </c>
       <c r="CU46" s="24">
-        <f>I46-CT46</f>
+        <f>I46-H46-SUM(M46:CR46)</f>
         <v/>
       </c>
       <c r="CV46" s="25">
-        <f>IF(I46=0,"",CT46/I46)</f>
+        <f>IF(I46=0,"",(H46+SUM(M46:CR46))/I46)</f>
         <v/>
       </c>
       <c r="CW46" s="26" t="n"/>
@@ -6852,15 +6887,15 @@
       <c r="CR47" s="21" t="n"/>
       <c r="CS47" s="21" t="n"/>
       <c r="CT47" s="24">
-        <f>SUM(M47:CR47)</f>
+        <f>H47+SUM(M47:CR47)</f>
         <v/>
       </c>
       <c r="CU47" s="24">
-        <f>I47-CT47</f>
+        <f>I47-H47-SUM(M47:CR47)</f>
         <v/>
       </c>
       <c r="CV47" s="25">
-        <f>IF(I47=0,"",CT47/I47)</f>
+        <f>IF(I47=0,"",(H47+SUM(M47:CR47))/I47)</f>
         <v/>
       </c>
       <c r="CW47" s="26" t="n"/>
@@ -6973,15 +7008,15 @@
       <c r="CR48" s="21" t="n"/>
       <c r="CS48" s="21" t="n"/>
       <c r="CT48" s="24">
-        <f>SUM(M48:CR48)</f>
+        <f>H48+SUM(M48:CR48)</f>
         <v/>
       </c>
       <c r="CU48" s="24">
-        <f>I48-CT48</f>
+        <f>I48-H48-SUM(M48:CR48)</f>
         <v/>
       </c>
       <c r="CV48" s="25">
-        <f>IF(I48=0,"",CT48/I48)</f>
+        <f>IF(I48=0,"",(H48+SUM(M48:CR48))/I48)</f>
         <v/>
       </c>
       <c r="CW48" s="26" t="n"/>
@@ -7094,15 +7129,15 @@
       <c r="CR49" s="21" t="n"/>
       <c r="CS49" s="21" t="n"/>
       <c r="CT49" s="24">
-        <f>SUM(M49:CR49)</f>
+        <f>H49+SUM(M49:CR49)</f>
         <v/>
       </c>
       <c r="CU49" s="24">
-        <f>I49-CT49</f>
+        <f>I49-H49-SUM(M49:CR49)</f>
         <v/>
       </c>
       <c r="CV49" s="25">
-        <f>IF(I49=0,"",CT49/I49)</f>
+        <f>IF(I49=0,"",(H49+SUM(M49:CR49))/I49)</f>
         <v/>
       </c>
       <c r="CW49" s="26" t="n"/>
@@ -7215,15 +7250,15 @@
       <c r="CR50" s="21" t="n"/>
       <c r="CS50" s="21" t="n"/>
       <c r="CT50" s="24">
-        <f>SUM(M50:CR50)</f>
+        <f>H50+SUM(M50:CR50)</f>
         <v/>
       </c>
       <c r="CU50" s="24">
-        <f>I50-CT50</f>
+        <f>I50-H50-SUM(M50:CR50)</f>
         <v/>
       </c>
       <c r="CV50" s="25">
-        <f>IF(I50=0,"",CT50/I50)</f>
+        <f>IF(I50=0,"",(H50+SUM(M50:CR50))/I50)</f>
         <v/>
       </c>
       <c r="CW50" s="26" t="n"/>
@@ -7336,15 +7371,15 @@
       <c r="CR51" s="21" t="n"/>
       <c r="CS51" s="21" t="n"/>
       <c r="CT51" s="24">
-        <f>SUM(M51:CR51)</f>
+        <f>H51+SUM(M51:CR51)</f>
         <v/>
       </c>
       <c r="CU51" s="24">
-        <f>I51-CT51</f>
+        <f>I51-H51-SUM(M51:CR51)</f>
         <v/>
       </c>
       <c r="CV51" s="25">
-        <f>IF(I51=0,"",CT51/I51)</f>
+        <f>IF(I51=0,"",(H51+SUM(M51:CR51))/I51)</f>
         <v/>
       </c>
       <c r="CW51" s="26" t="n"/>
